--- a/VBP.xlsx
+++ b/VBP.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/weij66_pfizer_com/Documents/桌面/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAC2A0F1-198A-4003-B388-01C09240E04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21600" windowHeight="9130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="75">
   <si>
     <t>省份</t>
   </si>
@@ -95,6 +89,9 @@
     <t>江苏</t>
   </si>
   <si>
+    <t>https://ybj.jiangsu.gov.cn/art/2026/3/20/art_74038_11747565.html</t>
+  </si>
+  <si>
     <t>内蒙古</t>
   </si>
   <si>
@@ -110,6 +107,9 @@
     <t>青海</t>
   </si>
   <si>
+    <t>https://ybj.qinghai.gov.cn/20260323/fe6b847ad29649bb9a7c595078fc9d68/c.html</t>
+  </si>
+  <si>
     <t>陕西</t>
   </si>
   <si>
@@ -173,135 +173,98 @@
     <t>https://www.baidu.com/link?url=aRwOFYoN7pfQOe2QI6yPKwwhRwpn6_EES1kXN-eRmNBAMeVdTCZOCIwhWryJtX_yazrCJ8f2b_9OcNPz1sdjPyzxXcZMDFKkdYXN1efDl8kpbTSkmwgcvpv-KD4uf7WX&amp;wd=&amp;eqid=8bf28a49005d0bdd0000000669c60474</t>
   </si>
   <si>
-    <t>是</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>山西</t>
+  </si>
+  <si>
+    <t>https://www.baidu.com/link?url=kzMHweXU-S_8DlczGAhlV4fNdJS3PbtOqGYeT4Yk3enKllhKI5Y_Gab2bwhYHeKxZDABb2b5IF53k_9EsnCqT9KL6o8gBhnWI8ywrGbhTdK&amp;wd=&amp;eqid=8bf28a49005d0bdd0000000669c60474</t>
+  </si>
+  <si>
+    <t>辽宁</t>
+  </si>
+  <si>
+    <t>https://ggzy.ln.gov.cn/yphc/tzgg/yp/202603/t20260325_5624418.html</t>
+  </si>
+  <si>
+    <t>海南</t>
+  </si>
+  <si>
+    <t>https://ybj.hainan.gov.cn/xxgk/tzgg/202603/t20260324_4048662.html</t>
+  </si>
+  <si>
+    <t>云南</t>
+  </si>
+  <si>
+    <t>https://ylbz.yn.gov.cn/index.php?c=show&amp;id=6087</t>
+  </si>
+  <si>
+    <t>新疆</t>
+  </si>
+  <si>
+    <t>https://ylbzj.xinjiang.gov.cn/ylbzj/tzgg/202603/79b14d980bc3451aa1d353aed3fe5f14.shtml</t>
+  </si>
+  <si>
+    <t>吉林</t>
+  </si>
+  <si>
+    <t>http://www.ggzyzx.jl.gov.cn/jyxx/yxcg/yp/202603/t20260326_3598097.html</t>
   </si>
   <si>
     <t>上海</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.smpaa.cn/xxgk/gggs/2026/03/30/20678.shtml</t>
+  </si>
+  <si>
+    <t>宁夏</t>
+  </si>
+  <si>
+    <t>https://ylbz.nx.gov.cn/zfxxgk/fdzdgknr/tzgg/202603/t20260330_5205727.html</t>
   </si>
   <si>
     <t>福建</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ybj.fujian.gov.cn/zfxxgkzl/fdzdgknr/qtyzdgkzfxx/202603/t20260331_7117591.htm</t>
   </si>
   <si>
     <t>贵州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>山西</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中选品完成任务量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.baidu.com/link?url=kzMHweXU-S_8DlczGAhlV4fNdJS3PbtOqGYeT4Yk3enKllhKI5Y_Gab2bwhYHeKxZDABb2b5IF53k_9EsnCqT9KL6o8gBhnWI8ywrGbhTdK&amp;wd=&amp;eqid=8bf28a49005d0bdd0000000669c60474</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>辽宁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ggzy.ln.gov.cn/yphc/tzgg/yp/202603/t20260325_5624418.html</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>海南</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ybj.hainan.gov.cn/xxgk/tzgg/202603/t20260324_4048662.html</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>云南</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ylbz.yn.gov.cn/index.php?c=show&amp;id=6087</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新疆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ylbzj.xinjiang.gov.cn/ylbzj/tzgg/202603/79b14d980bc3451aa1d353aed3fe5f14.shtml</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吉林</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://www.ggzyzx.jl.gov.cn/jyxx/yxcg/yp/202603/t20260326_3598097.html</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.smpaa.cn/xxgk/gggs/2026/03/30/20678.shtml</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>宁夏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ylbz.nx.gov.cn/zfxxgk/fdzdgknr/tzgg/202603/t20260330_5205727.html</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5:5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ybj.fujian.gov.cn/zfxxgkzl/fdzdgknr/qtyzdgkzfxx/202603/t20260331_7117591.htm</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>https://fuwu.pubs.ylbzj.guizhou.gov.cn/hsa-pass-hallEnter/index.html#/announcementDetail?type=5&amp;cont=%5Bobject%20Object%5D&amp;artContId=2038906299538653186</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>西藏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未提及明确比例限制</t>
   </si>
   <si>
     <t>https://ggfw.ylbzj.xizang.gov.cn/webPortal/detail.html?infoId=418643&amp;CatalogId=2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>甘肃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>https://ylbz.gansu.gov.cn/ylbzj/c107125/202603/174310591.shtml</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>未提及明确比例限制</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ybj.qinghai.gov.cn/20260323/fe6b847ad29649bb9a7c595078fc9d68/c.html</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ybj.jiangsu.gov.cn/art/2026/3/20/art_74038_11747565.html</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津</t>
+  </si>
+  <si>
+    <t>https://ylbz.tj.gov.cn/xxgk/zcfg/ybjwj/202605/t20260511_7296817.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,29 +281,150 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,8 +437,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -377,12 +647,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -393,166 +902,96 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -563,7 +1002,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -591,40 +1030,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -874,25 +1427,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.27272727272727" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="2" max="2" width="18.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="23.08984375" customWidth="1"/>
-    <col min="5" max="5" width="20.6328125" customWidth="1"/>
-    <col min="6" max="6" width="29.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.1818181818182" customWidth="1"/>
+    <col min="2" max="2" width="18.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="23.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="20.6363636363636" customWidth="1"/>
+    <col min="6" max="6" width="29.1818181818182" customWidth="1"/>
     <col min="7" max="7" width="109" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,7 +1468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,7 +1491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -961,7 +1514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -984,7 +1537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1007,7 +1560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1026,13 +1579,13 @@
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>15</v>
@@ -1050,12 +1603,12 @@
         <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>15</v>
@@ -1073,12 +1626,12 @@
         <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
@@ -1095,13 +1648,13 @@
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
@@ -1119,15 +1672,15 @@
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
@@ -1142,12 +1695,12 @@
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -1165,12 +1718,12 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
@@ -1188,12 +1741,12 @@
         <v>10</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -1211,12 +1764,12 @@
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
@@ -1234,12 +1787,12 @@
         <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
@@ -1257,12 +1810,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -1280,35 +1833,35 @@
         <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>15</v>
@@ -1326,346 +1879,360 @@
         <v>9</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="23" spans="1:7">
+      <c r="A23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="24" spans="1:7">
+      <c r="A24" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="25" spans="1:7">
+      <c r="A25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="26" spans="1:7">
+      <c r="A26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="27" spans="1:7">
+      <c r="A27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26" s="2" t="s">
+    <row r="28" spans="1:7">
+      <c r="A28" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27" s="2" t="s">
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G28" s="2" t="s">
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="C30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G16" r:id="rId13" location="/NewDetailContent?id=20260327162148000001&amp;type=jc&amp;title=%E4%BB%B7%E9%87%87%E5%85%AC%E5%91%8A" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="G23" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G22" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="G21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="G19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="G18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="G17" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="G25" r:id="rId22" xr:uid="{A94236D3-6EBE-4A24-AA28-16B688286C1A}"/>
-    <hyperlink ref="G26" r:id="rId23" xr:uid="{9A164DF1-F4F9-453A-AB21-FE4101BC223D}"/>
-    <hyperlink ref="G27" r:id="rId24" xr:uid="{C37FBA86-2B05-4F2D-A391-CB887C657507}"/>
-    <hyperlink ref="G28" r:id="rId25" xr:uid="{A51239B0-8032-4474-98A9-2D88FFBEC70B}"/>
-    <hyperlink ref="G29" r:id="rId26" location="/announcementDetail?type=5&amp;cont=%5Bobject%20Object%5D&amp;artContId=2038906299538653186" xr:uid="{8C97AE9A-57A3-4509-AE48-B7678398C96C}"/>
-    <hyperlink ref="G31" r:id="rId27" xr:uid="{FE5D617A-5B14-4D84-B55A-7529B509AA43}"/>
-    <hyperlink ref="G30" r:id="rId28" xr:uid="{053845BB-ED93-48B9-83FF-4DDE2407C7B4}"/>
-    <hyperlink ref="G9" r:id="rId29" xr:uid="{CAF155F7-BBA2-4A28-82A1-5C7240D59555}"/>
-    <hyperlink ref="G6" r:id="rId30" xr:uid="{09D16348-CBC6-49AC-927A-1525313777ED}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://ylbz.henan.gov.cn/2026/03-17/3334895.html"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://ybj.jiangxi.gov.cn/jxsylbzj/col/col28422/content/content_2034506018129960960.html"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://ggzyjyw.hlj.gov.cn/jyfwdt/003002/003002005/003002005004/20260319/b0bcdfd2-4f0c-4b99-b7bd-e397315c4a08.html"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://hsa.gd.gov.cn/zwgk/content/post_4872810.html"/>
+    <hyperlink ref="G7" r:id="rId5" display="https://ylbzj.nmg.gov.cn/yycgw/ycw_tzgg/ycw_yp/202603/t20260320_2877093.html"/>
+    <hyperlink ref="G8" r:id="rId6" display="http://ybj.gxzf.gov.cn/zfxxgkzl/zcfg/zcfg_9912/bmwj/gybh/t27372844.shtml"/>
+    <hyperlink ref="G10" r:id="rId7" display="https://ybj.shaanxi.gov.cn/zfxxgk/fdzdgknr/zcwj/202603/t20260320_3623441.html"/>
+    <hyperlink ref="G11" r:id="rId8" display="https://ybj.beijing.gov.cn/zczxs/2020_ycgga/202603/t20260326_4566984.html"/>
+    <hyperlink ref="G12" r:id="rId9" display="https://ylbzj.hebei.gov.cn/cms/content/5060"/>
+    <hyperlink ref="G13" r:id="rId10" display="http://ybj.zj.gov.cn/col/col1229225636/art/2026/art_5c4e489847754be485d5c823a5d8f2c9.html"/>
+    <hyperlink ref="G14" r:id="rId11" display="https://ybj.ah.gov.cn/public/7071/150476591.html"/>
+    <hyperlink ref="G15" r:id="rId12" display="http://ybj.shandong.gov.cn/art/2026/3/26/art_65415_10320565.html"/>
+    <hyperlink ref="G16" r:id="rId13" location="/NewDetailContent?id=20260327162148000001&amp;type=jc&amp;title=%E4%BB%B7%E9%87%87%E5%85%AC%E5%91%8A" display="https://ybj.hubei.gov.cn/hubeiHallSt/web/hallEnter/#/NewDetailContent?id=20260327162148000001&amp;type=jc&amp;title=%E4%BB%B7%E9%87%87%E5%85%AC%E5%91%8A"/>
+    <hyperlink ref="G24" r:id="rId14" display="https://ylbzj.xinjiang.gov.cn/ylbzj/tzgg/202603/79b14d980bc3451aa1d353aed3fe5f14.shtml"/>
+    <hyperlink ref="G23" r:id="rId15" display="https://ylbz.yn.gov.cn/index.php?c=show&amp;id=6087"/>
+    <hyperlink ref="G22" r:id="rId16" display="https://ybj.hainan.gov.cn/xxgk/tzgg/202603/t20260324_4048662.html"/>
+    <hyperlink ref="G21" r:id="rId17" display="https://ggzy.ln.gov.cn/yphc/tzgg/yp/202603/t20260325_5624418.html"/>
+    <hyperlink ref="G20" r:id="rId18" display="https://www.baidu.com/link?url=kzMHweXU-S_8DlczGAhlV4fNdJS3PbtOqGYeT4Yk3enKllhKI5Y_Gab2bwhYHeKxZDABb2b5IF53k_9EsnCqT9KL6o8gBhnWI8ywrGbhTdK&amp;wd=&amp;eqid=8bf28a49005d0bdd0000000669c60474"/>
+    <hyperlink ref="G19" r:id="rId19" display="https://www.baidu.com/link?url=aRwOFYoN7pfQOe2QI6yPKwwhRwpn6_EES1kXN-eRmNBAMeVdTCZOCIwhWryJtX_yazrCJ8f2b_9OcNPz1sdjPyzxXcZMDFKkdYXN1efDl8kpbTSkmwgcvpv-KD4uf7WX&amp;wd=&amp;eqid=8bf28a49005d0bdd0000000669c60474"/>
+    <hyperlink ref="G18" r:id="rId20" display="https://ylbzj.cq.gov.cn/zwgk_535/gstz/202603/t20260324_15562698.html"/>
+    <hyperlink ref="G17" r:id="rId21" display="https://ybj.hunan.gov.cn/ybj/first113541/firstF/f3113607/202603/t20260330_33943868.html"/>
+    <hyperlink ref="G25" r:id="rId22" display="http://www.ggzyzx.jl.gov.cn/jyxx/yxcg/yp/202603/t20260326_3598097.html"/>
+    <hyperlink ref="G26" r:id="rId23" display="https://www.smpaa.cn/xxgk/gggs/2026/03/30/20678.shtml"/>
+    <hyperlink ref="G27" r:id="rId24" display="https://ylbz.nx.gov.cn/zfxxgk/fdzdgknr/tzgg/202603/t20260330_5205727.html"/>
+    <hyperlink ref="G28" r:id="rId25" display="https://ybj.fujian.gov.cn/zfxxgkzl/fdzdgknr/qtyzdgkzfxx/202603/t20260331_7117591.htm"/>
+    <hyperlink ref="G29" r:id="rId26" location="/announcementDetail?type=5&amp;cont=%5Bobject%20Object%5D&amp;artContId=2038906299538653186" display="https://fuwu.pubs.ylbzj.guizhou.gov.cn/hsa-pass-hallEnter/index.html#/announcementDetail?type=5&amp;cont=%5Bobject%20Object%5D&amp;artContId=2038906299538653186"/>
+    <hyperlink ref="G31" r:id="rId27" display="https://ylbz.gansu.gov.cn/ylbzj/c107125/202603/174310591.shtml"/>
+    <hyperlink ref="G30" r:id="rId28" display="https://ggfw.ylbzj.xizang.gov.cn/webPortal/detail.html?infoId=418643&amp;CatalogId=2"/>
+    <hyperlink ref="G9" r:id="rId29" display="https://ybj.qinghai.gov.cn/20260323/fe6b847ad29649bb9a7c595078fc9d68/c.html"/>
+    <hyperlink ref="G6" r:id="rId30" display="https://ybj.jiangsu.gov.cn/art/2026/3/20/art_74038_11747565.html"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>